--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -74,24 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">[{"type":1,"resistance":0.0},{"type":2,"resistance":0.0},{"type":3,"resistance":0.0},{"type":4,"resistance":0.0}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"skillId":2002,"cooldown":4.0,"damageMultiplier":1.5}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"type":1,"resistance":0.25},{"type":2,"resistance":0.2},{"type":3,"resistance":0.35},{"type":4,"resistance":0.25}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"skillId":2005,"cooldown":5.0,"damageMultiplier":2.0},{"skillId":2006,"cooldown":7.0,"damageMultiplier":1.25},{"skillId":2007,"cooldown":6.0,"damageMultiplier":1.0}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"type":1,"resistance":0.5},{"type":2,"resistance":0.4},{"type":3,"resistance":0.6},{"type":4,"resistance":0.5}]</t>
   </si>
 </sst>
 </file>
@@ -372,7 +354,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.63"/>
@@ -431,7 +413,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>14</v>
@@ -473,94 +455,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
